--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Domain_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Domain_by_Sample_name.xlsx
@@ -388,10 +388,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999998</v>
+        <v>99.9999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1.39257526152506</v>
+        <v>1.39307839096705</v>
       </c>
     </row>
   </sheetData>
@@ -427,10 +427,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999998</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>2.53816576692554</v>
+        <v>2.54700411476332</v>
       </c>
     </row>
   </sheetData>
@@ -466,10 +466,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9999999999997</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.622953572773905</v>
+        <v>0.622880861117178</v>
       </c>
     </row>
   </sheetData>
